--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_250_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_250_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2003</v>
+        <v>6.1074</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7416</v>
+        <v>5.4808</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4586</v>
+        <v>0.6267</v>
       </c>
       <c r="G2" t="n">
         <v>5.3613</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0581</v>
+        <v>-1.151</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0297</v>
+        <v>-0.2906</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0284</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>3.7527</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1523</v>
+        <v>3.5872</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9856</v>
+        <v>2.5884</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1668</v>
+        <v>0.9987</v>
       </c>
       <c r="G3" t="n">
         <v>1.9785</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1892</v>
+        <v>0.624</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3383</v>
+        <v>-0.0589</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8509</v>
+        <v>0.6829</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6267</v>
+        <v>2.9197</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2871</v>
+        <v>0.8153</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3396</v>
+        <v>2.1044</v>
       </c>
       <c r="G4" t="n">
         <v>0.4001</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2087</v>
+        <v>-0.4984</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8417</v>
+        <v>0.3699</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.633</v>
+        <v>-0.8683</v>
       </c>
       <c r="V4" t="n">
         <v>0.9304</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4784</v>
+        <v>2.5338</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9267</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5517</v>
+        <v>1.6189</v>
       </c>
       <c r="G5" t="n">
         <v>0.3818</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5245</v>
+        <v>0.5799</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1845</v>
+        <v>-0.1964</v>
       </c>
       <c r="U5" t="n">
-        <v>0.709</v>
+        <v>0.7762</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2836</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.0786</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5606</v>
+        <v>-0.6802</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4789</v>
+        <v>0.6016</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3636</v>
+        <v>-1.7189</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0323</v>
+        <v>-2.0803</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3312</v>
+        <v>0.3614</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0368</v>
+        <v>-0.8966</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1.5223</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>0.6257</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4004</v>
+        <v>-0.8223</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0323</v>
+        <v>-0.5581</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.368</v>
+        <v>-0.2643</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8153</v>
+        <v>0.4806</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5623</v>
+        <v>0.2164</v>
       </c>
       <c r="U6" t="n">
-        <v>0.253</v>
+        <v>0.2642</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8663</v>
+        <v>-0.7477</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5687</v>
+        <v>-0.9578</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7025</v>
+        <v>0.2101</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7189</v>
+        <v>-0.3636</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0803</v>
+        <v>-0.0323</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3614</v>
+        <v>-0.3312</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8966</v>
+        <v>0.0368</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5223</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6257</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8223</v>
+        <v>-0.4004</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5581</v>
+        <v>-0.0323</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2643</v>
+        <v>-0.368</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3071</v>
+        <v>0.1494</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6721</v>
+        <v>0.1652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3651</v>
+        <v>-0.0158</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4786</v>
+        <v>-1.5194</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6911</v>
+        <v>-1.8327</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2125</v>
+        <v>0.3133</v>
       </c>
       <c r="G8" t="n">
         <v>-3.7555</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8852</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5272</v>
+        <v>0.3855</v>
       </c>
       <c r="U8" t="n">
-        <v>0.358</v>
+        <v>0.4589</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5973</v>
+        <v>-1.5517</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1302</v>
+        <v>-0.6135</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4671</v>
+        <v>-0.9382</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6991</v>
+        <v>2.916</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2005</v>
+        <v>1.4874</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4986</v>
+        <v>1.4286</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1058</v>
+        <v>4.203</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6076</v>
+        <v>2.4031</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5018</v>
+        <v>1.7999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5933</v>
+        <v>-1.287</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4071</v>
+        <v>-0.9157</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0004</v>
+        <v>-0.3713</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2899</v>
+        <v>0.174</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8338</v>
+        <v>-0.2317</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1237</v>
+        <v>0.4057</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0793</v>
+        <v>-1.8361</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4212</v>
+        <v>-1.5706</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3419</v>
+        <v>-0.2654</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9071</v>
+        <v>-2.6991</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3818</v>
+        <v>-2.2005</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5253</v>
+        <v>-0.4986</v>
       </c>
       <c r="J10" t="n">
+        <v>-2.1058</v>
+      </c>
+      <c r="K10" t="n">
         <v>-2.6076</v>
       </c>
-      <c r="K10" t="n">
-        <v>-1.8213</v>
-      </c>
       <c r="L10" t="n">
-        <v>-0.7863</v>
+        <v>0.5018</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7005</v>
+        <v>-0.5933</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4395</v>
+        <v>0.4071</v>
       </c>
       <c r="O10" t="n">
-        <v>0.261</v>
+        <v>-1.0004</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5236</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3462</v>
+        <v>0.3934</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1775</v>
+        <v>-0.9221</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8078</v>
+        <v>-2.1077</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2853</v>
+        <v>-3.3151</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5225</v>
+        <v>1.2074</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6586</v>
+        <v>-1.9071</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5929</v>
+        <v>-1.3818</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2515</v>
+        <v>-0.5253</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3941</v>
+        <v>-2.6076</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9677</v>
+        <v>-1.8213</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3618</v>
+        <v>-0.7863</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2645</v>
+        <v>0.7005</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3748</v>
+        <v>0.4395</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1103</v>
+        <v>0.261</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2292</v>
+        <v>0.4953</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.731</v>
+        <v>0.4523</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4982</v>
+        <v>0.0431</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.933</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.877</v>
+        <v>-2.2195</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.502</v>
+        <v>-1.4282</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3751</v>
+        <v>-0.7913</v>
       </c>
       <c r="G12" t="n">
-        <v>2.916</v>
+        <v>0.6586</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4874</v>
+        <v>-0.5929</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4286</v>
+        <v>1.2515</v>
       </c>
       <c r="J12" t="n">
-        <v>4.203</v>
+        <v>0.3941</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4031</v>
+        <v>-0.9677</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7999</v>
+        <v>1.3618</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.287</v>
+        <v>0.2645</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9157</v>
+        <v>0.3748</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3713</v>
+        <v>-0.1103</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.7112</v>
+        <v>0.6959</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.7988</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1514</v>
+        <v>-0.6409</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1202</v>
+        <v>0.1261</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0312</v>
+        <v>-0.767</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9304</v>
+        <v>-2.933</v>
       </c>
       <c r="W12" t="n">
-        <v>1.214</v>
+        <v>-0.7886</v>
       </c>
       <c r="X12" t="n">
         <v>-2.1444</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.918</v>
+        <v>-4.0952</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.4689</v>
+        <v>-4.8477</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-3.7585</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8038</v>
+        <v>-0.981</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.731</v>
+        <v>-0.1098</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0728</v>
+        <v>-0.8711</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2836</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.248299999999999</v>
+        <v>0.9922000000000022</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.687</v>
+        <v>-5.446499999999999</v>
       </c>
       <c r="F14" t="n">
         <v>6.438700000000001</v>
@@ -1525,19 +1525,19 @@
         <v>-5.644</v>
       </c>
       <c r="L14" t="n">
-        <v>7.928699999999999</v>
+        <v>7.928700000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-4.791300000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8643</v>
+        <v>-1.864300000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-2.9268</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>1.159800000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2367</v>
@@ -1546,22 +1546,22 @@
         <v>17.3965</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.693000000000001</v>
+        <v>-0.4525</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.019</v>
+        <v>1.2214</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6738</v>
+        <v>-1.6737</v>
       </c>
       <c r="V14" t="n">
         <v>2.7912</v>
       </c>
       <c r="W14" t="n">
-        <v>7.284000000000001</v>
+        <v>7.284</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.4928</v>
+        <v>-4.492800000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.393000000000001</v>
+        <v>10.2409</v>
       </c>
       <c r="E15" t="n">
-        <v>7.4937</v>
+        <v>8.083500000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8993</v>
+        <v>2.1574</v>
       </c>
       <c r="G15" t="n">
         <v>8.3108</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5856</v>
+        <v>0.2623</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8136</v>
+        <v>-0.2238</v>
       </c>
       <c r="U15" t="n">
-        <v>0.228</v>
+        <v>0.4861</v>
       </c>
       <c r="V15" t="n">
         <v>4.6831</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7358</v>
+        <v>4.6229</v>
       </c>
       <c r="E16" t="n">
-        <v>1.647</v>
+        <v>1.1752</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0888</v>
+        <v>3.4477</v>
       </c>
       <c r="G16" t="n">
         <v>2.6014</v>
@@ -1702,13 +1702,13 @@
         <v>3.0154</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.4854</v>
       </c>
       <c r="T16" t="n">
-        <v>0.311</v>
+        <v>-0.1608</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2873</v>
+        <v>0.6462</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9526</v>
+        <v>2.245</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2817</v>
+        <v>1.3381</v>
       </c>
       <c r="G17" t="n">
         <v>-0.008500000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4793</v>
+        <v>0.7716</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4086</v>
+        <v>-0.1727</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8878</v>
+        <v>0.9443</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7438</v>
+        <v>0.1153</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7098</v>
+        <v>-0.9415</v>
       </c>
       <c r="F18" t="n">
-        <v>1.034</v>
+        <v>1.0568</v>
       </c>
       <c r="G18" t="n">
         <v>1.1994</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3125</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5558</v>
+        <v>0.9045</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2434</v>
+        <v>-0.2205</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.16</v>
+        <v>-0.3384</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5512</v>
+        <v>-1.6691</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7111</v>
+        <v>1.3307</v>
       </c>
       <c r="G19" t="n">
         <v>2.298</v>
@@ -1936,13 +1936,13 @@
         <v>2.3195</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4418</v>
+        <v>0.9434</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4604</v>
+        <v>0.3424</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.601</v>
       </c>
       <c r="V19" t="n">
         <v>-3.5799</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8853</v>
+        <v>-0.6698</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0683</v>
+        <v>-2.414</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8169999999999999</v>
+        <v>1.7442</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5488</v>
+        <v>-1.6652</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9699</v>
+        <v>-0.0625</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5788</v>
+        <v>-1.6027</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7695</v>
+        <v>-2.0015</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7695</v>
+        <v>-0.9306</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.0709</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7792</v>
+        <v>0.3363</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2004</v>
+        <v>0.8681</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5788</v>
+        <v>-0.5319</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5685</v>
+        <v>-0.0226</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2987</v>
+        <v>-0.1806</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2697</v>
+        <v>0.1579</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.129</v>
+        <v>-1.3069</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1217</v>
+        <v>-0.7144</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9927</v>
+        <v>-0.5925</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6652</v>
+        <v>-1.5488</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0625</v>
+        <v>-0.9699</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6027</v>
+        <v>-0.5788</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0015</v>
+        <v>-0.7695</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9306</v>
+        <v>-0.7695</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0709</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3363</v>
+        <v>-0.7792</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8681</v>
+        <v>-0.2004</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5319</v>
+        <v>-0.5788</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4818</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8883</v>
+        <v>0.0551</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5935</v>
+        <v>-0.0452</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.23</v>
+        <v>-1.4379</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2567</v>
+        <v>-2.431</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0267</v>
+        <v>0.9931</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9006</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6515</v>
+        <v>0.1406</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8215</v>
+        <v>0.0042</v>
       </c>
       <c r="U22" t="n">
-        <v>0.17</v>
+        <v>0.1364</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2582</v>
+        <v>-1.7863</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7221</v>
+        <v>-1.2502</v>
       </c>
       <c r="F23" t="n">
         <v>-0.5361</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3066</v>
+        <v>0.1652</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1494</v>
+        <v>0.3224</v>
       </c>
       <c r="U23" t="n">
         <v>-0.1573</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4569</v>
+        <v>-3.5299</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7914</v>
+        <v>-2.0889</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6655</v>
+        <v>-1.4411</v>
       </c>
       <c r="G24" t="n">
         <v>-1.629</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6412</v>
+        <v>0.5682</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7616</v>
+        <v>0.4641</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1204</v>
+        <v>0.1041</v>
       </c>
       <c r="V24" t="n">
         <v>-2.933</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7776</v>
+        <v>-5.3337</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.449</v>
+        <v>-5.0951</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3286</v>
+        <v>-0.2386</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1996</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1863</v>
+        <v>0.2576</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0351</v>
+        <v>0.3187</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1511</v>
+        <v>-0.0611</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5361</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.248200000000003</v>
+        <v>2.821199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.438999999999999</v>
+        <v>-6.438700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>7.687100000000003</v>
+        <v>9.2597</v>
       </c>
       <c r="G26" t="n">
-        <v>2.506399999999999</v>
+        <v>2.506400000000001</v>
       </c>
       <c r="H26" t="n">
         <v>7.5083</v>
@@ -2467,7 +2467,7 @@
         <v>-2.2847</v>
       </c>
       <c r="N26" t="n">
-        <v>5.644</v>
+        <v>5.643999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-7.928800000000001</v>
@@ -2482,13 +2482,13 @@
         <v>16.2368</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6928</v>
+        <v>4.265600000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6736</v>
+        <v>1.6735</v>
       </c>
       <c r="U26" t="n">
-        <v>1.0191</v>
+        <v>2.591899999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-2.7913</v>
